--- a/产品研发进度.xlsx
+++ b/产品研发进度.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>序号</t>
   </si>
@@ -1275,6 +1275,9 @@
       <c r="C10" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="11" ht="28.8" spans="1:8">
       <c r="A11">
@@ -1297,6 +1300,9 @@
       <c r="C12" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>34</v>
       </c>
@@ -1340,7 +1346,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8 E13 E14 E1:E7 E9:E12 E15:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10 E11 E12 E1:E9 E13:E1048576">
       <formula1>"已修复,未修复"</formula1>
     </dataValidation>
   </dataValidations>
